--- a/majMapping/ig/FRObservationResultLMCDAFHIR.xlsx
+++ b/majMapping/ig/FRObservationResultLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:52:25+00:00</t>
+    <t>2026-10-08T12:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/majMapping/ig/FRObservationResultLMCDAFHIR.xlsx
+++ b/majMapping/ig/FRObservationResultLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:48:01+00:00</t>
+    <t>2026-10-08T13:13:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
